--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.17-authentication-information/WKBK/90_workbooks/ISMS-IMP-A.5.17.3_Password_System_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.17-authentication-information/WKBK/90_workbooks/ISMS-IMP-A.5.17.3_Password_System_Assessment_20260208.xlsx
@@ -851,7 +851,7 @@
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Azure AD SSO</t>
+          <t>Microsoft Entra ID (formerly Azure AD) SSO</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Azure AD</t>
+          <t>Microsoft Entra ID (formerly Azure AD)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Azure AD conditional access policies</t>
+          <t>Microsoft Entra ID (formerly Azure AD) conditional access policies</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
